--- a/spiderJapanese/登录数据.xlsx
+++ b/spiderJapanese/登录数据.xlsx
@@ -1053,8 +1053,8 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
+      <c r="E2" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1078,8 +1078,8 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E3" t="b">
-        <v>0</v>
+      <c r="E3" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1103,6 +1103,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -1125,6 +1128,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -1147,6 +1153,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -1169,6 +1178,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -1191,6 +1203,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
@@ -1213,6 +1228,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
@@ -1235,6 +1253,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
@@ -1257,6 +1278,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -1279,6 +1303,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -1301,6 +1328,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -1323,6 +1353,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -1345,6 +1378,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -1367,6 +1403,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
@@ -1389,6 +1428,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -1411,6 +1453,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -1433,6 +1478,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
@@ -1455,6 +1503,9 @@
           <t>Ha112211</t>
         </is>
       </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
@@ -1476,6 +1527,9 @@
         <is>
           <t>Ha112211</t>
         </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/spiderJapanese/登录数据.xlsx
+++ b/spiderJapanese/登录数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19635" windowHeight="7575" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="E2" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1103,7 +1103,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1203,7 +1203,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="0" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1303,7 +1303,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1428,7 +1428,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/spiderJapanese/登录数据.xlsx
+++ b/spiderJapanese/登录数据.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="19635" windowHeight="7575" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1031,6 +1031,11 @@
           <t>登录状态</t>
         </is>
       </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>cookie</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1054,7 +1059,10 @@
         </is>
       </c>
       <c r="E2" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1079,7 +1087,10 @@
         </is>
       </c>
       <c r="E3" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1106,6 +1117,9 @@
       <c r="E4" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
@@ -1131,6 +1145,9 @@
       <c r="E5" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
@@ -1156,6 +1173,9 @@
       <c r="E6" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
@@ -1179,7 +1199,10 @@
         </is>
       </c>
       <c r="E7" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1204,7 +1227,10 @@
         </is>
       </c>
       <c r="E8" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1229,7 +1255,10 @@
         </is>
       </c>
       <c r="E9" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1254,7 +1283,10 @@
         </is>
       </c>
       <c r="E10" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1281,6 +1313,9 @@
       <c r="E11" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
@@ -1306,6 +1341,9 @@
       <c r="E12" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
@@ -1331,6 +1369,9 @@
       <c r="E13" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
@@ -1356,6 +1397,9 @@
       <c r="E14" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
@@ -1381,6 +1425,9 @@
       <c r="E15" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
@@ -1406,6 +1453,9 @@
       <c r="E16" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
@@ -1431,6 +1481,9 @@
       <c r="E17" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
@@ -1456,6 +1509,9 @@
       <c r="E18" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
@@ -1481,6 +1537,9 @@
       <c r="E19" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
@@ -1506,6 +1565,9 @@
       <c r="E20" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
@@ -1529,6 +1591,9 @@
         </is>
       </c>
       <c r="E21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="b">
         <v>0</v>
       </c>
     </row>

--- a/spiderJapanese/登录数据.xlsx
+++ b/spiderJapanese/登录数据.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="306">
   <si>
     <t>编号</t>
   </si>
@@ -46,7 +46,871 @@
     <t>登录状态</t>
   </si>
   <si>
-    <t>cookie</t>
+    <t>H607</t>
+  </si>
+  <si>
+    <t>LoganWallace4405@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/976fab075d6a0126/LoganWallace4405%40outlook.com</t>
+  </si>
+  <si>
+    <t>Ha112211</t>
+  </si>
+  <si>
+    <t>H608</t>
+  </si>
+  <si>
+    <t>DanteIrvine8629@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/4f8abeb02aa34166/DanteIrvine8629%40outlook.com</t>
+  </si>
+  <si>
+    <t>H609</t>
+  </si>
+  <si>
+    <t>CherylMora4203@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/c3d13e1792ca40f8/CherylMora4203%40outlook.com</t>
+  </si>
+  <si>
+    <t>H610</t>
+  </si>
+  <si>
+    <t>MollyNunes2030@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a44ba26ecfcf8260/MollyNunes2030%40outlook.com</t>
+  </si>
+  <si>
+    <t>H611</t>
+  </si>
+  <si>
+    <t>JoeHines3731@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/2ba70e2f8a41697c/JoeHines3731%40outlook.com</t>
+  </si>
+  <si>
+    <t>H612</t>
+  </si>
+  <si>
+    <t>LawrenceStevens6421@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a93be6a787515537/LawrenceStevens6421%40outlook.com</t>
+  </si>
+  <si>
+    <t>H613</t>
+  </si>
+  <si>
+    <t>KellyMunro1477@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/95703dec3be3eb0a/KellyMunro1477%40outlook.com</t>
+  </si>
+  <si>
+    <t>H614</t>
+  </si>
+  <si>
+    <t>JuneMelton5318@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/97b81f7a8ebded3c/JuneMelton5318%40outlook.com</t>
+  </si>
+  <si>
+    <t>H615</t>
+  </si>
+  <si>
+    <t>LyraFrost9345@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/d885bf3213ad91a8/LyraFrost9345%40outlook.com</t>
+  </si>
+  <si>
+    <t>H616</t>
+  </si>
+  <si>
+    <t>IslaBlake1504@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/b7267ae761b3327f/IslaBlake1504%40outlook.com</t>
+  </si>
+  <si>
+    <t>H617</t>
+  </si>
+  <si>
+    <t>LylaAtkins7594@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/e201f4b62ea2255f/LylaAtkins7594%40outlook.com</t>
+  </si>
+  <si>
+    <t>H618</t>
+  </si>
+  <si>
+    <t>JaydenGregory3733@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/0b61165dd2150312/JaydenGregory3733%40outlook.com</t>
+  </si>
+  <si>
+    <t>H619</t>
+  </si>
+  <si>
+    <t>LincolnMize1551@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/783622d9b8364743/LincolnMize1551%40outlook.com</t>
+  </si>
+  <si>
+    <t>H620</t>
+  </si>
+  <si>
+    <t>CarolineAlexander7335@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/820583b7405f2591/CarolineAlexander7335%40outlook.com</t>
+  </si>
+  <si>
+    <t>H621</t>
+  </si>
+  <si>
+    <t>ElizabethMontoya4908@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/124262e54acbdacc/ElizabethMontoya4908%40outlook.com</t>
+  </si>
+  <si>
+    <t>H622</t>
+  </si>
+  <si>
+    <t>MackenzieMercer6362@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/03bbfde8a9ac5b08/MackenzieMercer6362%40outlook.com</t>
+  </si>
+  <si>
+    <t>H623</t>
+  </si>
+  <si>
+    <t>EmmaWiggins6113@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/85d3d404262fb756/EmmaWiggins6113%40outlook.com</t>
+  </si>
+  <si>
+    <t>H624</t>
+  </si>
+  <si>
+    <t>SeanGeddes1993@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/434342602b7ed024/SeanGeddes1993%40outlook.com</t>
+  </si>
+  <si>
+    <t>H625</t>
+  </si>
+  <si>
+    <t>DeanSimpson2150@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/15c7802983d3b125/DeanSimpson2150%40outlook.com</t>
+  </si>
+  <si>
+    <t>H626</t>
+  </si>
+  <si>
+    <t>WyattYoung2899@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/1116d69ded6e51dd/WyattYoung2899%40outlook.com</t>
+  </si>
+  <si>
+    <t>H627</t>
+  </si>
+  <si>
+    <t>HunterMcDonald7149@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/5f0dcc3f5aea4971/HunterMcDonald7149%40outlook.com</t>
+  </si>
+  <si>
+    <t>H628</t>
+  </si>
+  <si>
+    <t>ZoeBell7571@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/83925594ad0cfa42/ZoeBell7571%40outlook.com</t>
+  </si>
+  <si>
+    <t>H629</t>
+  </si>
+  <si>
+    <t>AnnaFerguson1513@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/c0bc17370d47e8b9/AnnaFerguson1513%40outlook.com</t>
+  </si>
+  <si>
+    <t>H630</t>
+  </si>
+  <si>
+    <t>WilliamPickering7944@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/ef0f03f5d771ff23/WilliamPickering7944%40outlook.com</t>
+  </si>
+  <si>
+    <t>H631</t>
+  </si>
+  <si>
+    <t>ZacharyBenson4213@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/0ce5a6063f48a3dd/ZacharyBenson4213%40outlook.com</t>
+  </si>
+  <si>
+    <t>H632</t>
+  </si>
+  <si>
+    <t>LeiaLight4639@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/abf539e7967f47de/LeiaLight4639%40outlook.com</t>
+  </si>
+  <si>
+    <t>H633</t>
+  </si>
+  <si>
+    <t>RyanClarke8467@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a7a55f2aa8d34485/RyanClarke8467%40outlook.com</t>
+  </si>
+  <si>
+    <t>H634</t>
+  </si>
+  <si>
+    <t>HugoFlynn6905@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/adcccd00464b1954/HugoFlynn6905%40outlook.com</t>
+  </si>
+  <si>
+    <t>H635</t>
+  </si>
+  <si>
+    <t>MayaMoriarty5263@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/d28aa5778385cfc1/MayaMoriarty5263%40outlook.com</t>
+  </si>
+  <si>
+    <t>H636</t>
+  </si>
+  <si>
+    <t>AustinMorrison2327@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/ca36692e13ded639/AustinMorrison2327%40outlook.com</t>
+  </si>
+  <si>
+    <t>H637</t>
+  </si>
+  <si>
+    <t>VioletRomero7746@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/38d69e2a356d3778/VioletRomero7746%40outlook.com</t>
+  </si>
+  <si>
+    <t>H638</t>
+  </si>
+  <si>
+    <t>AliceWashington8906@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/bac107909e0132eb/AliceWashington8906%40outlook.com</t>
+  </si>
+  <si>
+    <t>H639</t>
+  </si>
+  <si>
+    <t>VictoriaNeuman9809@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/338c6a11a87c3685/VictoriaNeuman9809%40outlook.com</t>
+  </si>
+  <si>
+    <t>H640</t>
+  </si>
+  <si>
+    <t>LanaWashington2966@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/5ec8fd3cb5e3c2ef/LanaWashington2966%40outlook.com</t>
+  </si>
+  <si>
+    <t>H641</t>
+  </si>
+  <si>
+    <t>WillowMatthews2848@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/3b1935181644bf7d/WillowMatthews2848%40outlook.com</t>
+  </si>
+  <si>
+    <t>H642</t>
+  </si>
+  <si>
+    <t>AbigailLaw5534@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/e081aa542842c22c/AbigailLaw5534%40outlook.com</t>
+  </si>
+  <si>
+    <t>H643</t>
+  </si>
+  <si>
+    <t>DavidMcLaughlin9343@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/fb3582b117260ff1/DavidMcLaughlin9343%40outlook.com</t>
+  </si>
+  <si>
+    <t>H644</t>
+  </si>
+  <si>
+    <t>SophiaBell7584@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/fbb385a074704150/SophiaBell7584%40outlook.com</t>
+  </si>
+  <si>
+    <t>H645</t>
+  </si>
+  <si>
+    <t>RuthCooper5419@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/b7f114faa66e3244/RuthCooper5419%40outlook.com</t>
+  </si>
+  <si>
+    <t>H646</t>
+  </si>
+  <si>
+    <t>PiperDoherty9108@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/adc49bd54472a9b0/PiperDoherty9108%40outlook.com</t>
+  </si>
+  <si>
+    <t>H647</t>
+  </si>
+  <si>
+    <t>RachelNeff2533@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/d171718e17716cf3/RachelNeff2533%40outlook.com</t>
+  </si>
+  <si>
+    <t>H648</t>
+  </si>
+  <si>
+    <t>CarolynFowler4878@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/b3c6c1c00185a5c7/CarolynFowler4878%40outlook.com</t>
+  </si>
+  <si>
+    <t>H649</t>
+  </si>
+  <si>
+    <t>MarenMorales3274@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/18d8597929c74cd8/MarenMorales3274%40outlook.com</t>
+  </si>
+  <si>
+    <t>H650</t>
+  </si>
+  <si>
+    <t>LukeBenson2669@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/83b61b7f53661f16/LukeBenson2669%40outlook.com</t>
+  </si>
+  <si>
+    <t>H651</t>
+  </si>
+  <si>
+    <t>SavannahPollard8686@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/702f833310bc8da4/SavannahPollard8686%40outlook.com</t>
+  </si>
+  <si>
+    <t>H652</t>
+  </si>
+  <si>
+    <t>CarterCaufield7214@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/12c6023b8690a21b/CarterCaufield7214%40outlook.com</t>
+  </si>
+  <si>
+    <t>H653</t>
+  </si>
+  <si>
+    <t>AdonisMartin5227@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/7c57f33406c4857b/AdonisMartin5227%40outlook.com</t>
+  </si>
+  <si>
+    <t>H654</t>
+  </si>
+  <si>
+    <t>AsherHancock6386@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/97c973c0a69cb9fa/AsherHancock6386%40outlook.com</t>
+  </si>
+  <si>
+    <t>H655</t>
+  </si>
+  <si>
+    <t>AbelBaillie5326@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/448b723019d08459/AbelBaillie5326%40outlook.com</t>
+  </si>
+  <si>
+    <t>H656</t>
+  </si>
+  <si>
+    <t>LaylaPerry7131@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/e859b72901cb38f8/LaylaPerry7131%40outlook.com</t>
+  </si>
+  <si>
+    <t>H657</t>
+  </si>
+  <si>
+    <t>JordanPierce3119@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/4fa0bfd02f078af7/JordanPierce3119%40outlook.com</t>
+  </si>
+  <si>
+    <t>H658</t>
+  </si>
+  <si>
+    <t>RykerKelly1119@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/7c110d60bf69610a/RykerKelly1119%40outlook.com</t>
+  </si>
+  <si>
+    <t>H659</t>
+  </si>
+  <si>
+    <t>BenjaminWalsh3768@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/ff2d8b09fcdd6555/BenjaminWalsh3768%40outlook.com</t>
+  </si>
+  <si>
+    <t>H660</t>
+  </si>
+  <si>
+    <t>GraysonHume6696@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/383894259424b103/GraysonHume6696%40outlook.com</t>
+  </si>
+  <si>
+    <t>H661</t>
+  </si>
+  <si>
+    <t>LylaMoriarty3944@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/1fcf7637630df835/LylaMoriarty3944%40outlook.com</t>
+  </si>
+  <si>
+    <t>H662</t>
+  </si>
+  <si>
+    <t>JeremyCole5562@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/6ef58a88b4894c3a/JeremyCole5562%40outlook.com</t>
+  </si>
+  <si>
+    <t>H663</t>
+  </si>
+  <si>
+    <t>RyleeSoto6143@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/9aba92f09bcea28d/RyleeSoto6143%40outlook.com</t>
+  </si>
+  <si>
+    <t>H664</t>
+  </si>
+  <si>
+    <t>BeckettGomez6698@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/b64cf9d4732e1567/BeckettGomez6698%40outlook.com</t>
+  </si>
+  <si>
+    <t>H665</t>
+  </si>
+  <si>
+    <t>PeterNunn3902@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/6d31e04c3d1c1175/PeterNunn3902%40outlook.com</t>
+  </si>
+  <si>
+    <t>H666</t>
+  </si>
+  <si>
+    <t>MarthaNichols8455@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/ee0a1e079316ff94/MarthaNichols8455%40outlook.com</t>
+  </si>
+  <si>
+    <t>H667</t>
+  </si>
+  <si>
+    <t>IsiahBall8960@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/6528cd5fa058e61f/IsiahBall8960%40outlook.com</t>
+  </si>
+  <si>
+    <t>H668</t>
+  </si>
+  <si>
+    <t>MatthewNightingale5815@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/53aabb95400638a6/MatthewNightingale5815%40outlook.com</t>
+  </si>
+  <si>
+    <t>H669</t>
+  </si>
+  <si>
+    <t>DorothyReyes5813@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/5f36dc7d88f1d501/DorothyReyes5813%40outlook.com</t>
+  </si>
+  <si>
+    <t>H670</t>
+  </si>
+  <si>
+    <t>AveryBell8104@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/8e3498489bc3533e/AveryBell8104%40outlook.com</t>
+  </si>
+  <si>
+    <t>H671</t>
+  </si>
+  <si>
+    <t>RachelWilson2467@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/da9a8ba99e71a2ff/RachelWilson2467%40outlook.com</t>
+  </si>
+  <si>
+    <t>H672</t>
+  </si>
+  <si>
+    <t>LydiaKennedy7118@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/4bef06847e27b56d/LydiaKennedy7118%40outlook.com</t>
+  </si>
+  <si>
+    <t>H673</t>
+  </si>
+  <si>
+    <t>IsabellaMonroe8273@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/cb5144690e476600/IsabellaMonroe8273%40outlook.com</t>
+  </si>
+  <si>
+    <t>H674</t>
+  </si>
+  <si>
+    <t>BrendaLambert1930@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a56367f21d956b35/BrendaLambert1930%40outlook.com</t>
+  </si>
+  <si>
+    <t>H675</t>
+  </si>
+  <si>
+    <t>AdamMontgomery1569@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a5c405ae61e24be5/AdamMontgomery1569%40outlook.com</t>
+  </si>
+  <si>
+    <t>H676</t>
+  </si>
+  <si>
+    <t>GeraldBailey8446@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/fe14b32b113ead48/GeraldBailey8446%40outlook.com</t>
+  </si>
+  <si>
+    <t>H677</t>
+  </si>
+  <si>
+    <t>MayaCole6618@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/08c6ac7d75437e03/MayaCole6618%40outlook.com</t>
+  </si>
+  <si>
+    <t>H678</t>
+  </si>
+  <si>
+    <t>FelixMoody8890@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/544e699848eee95e/FelixMoody8890%40outlook.com</t>
+  </si>
+  <si>
+    <t>H679</t>
+  </si>
+  <si>
+    <t>RubyMason4966@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/42fe1b71338caa99/RubyMason4966%40outlook.com</t>
+  </si>
+  <si>
+    <t>H680</t>
+  </si>
+  <si>
+    <t>DavidBurns3205@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/943f6e8d70a54ab6/DavidBurns3205%40outlook.com</t>
+  </si>
+  <si>
+    <t>H681</t>
+  </si>
+  <si>
+    <t>ElianaCook6962@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/008a1face5b54d02/ElianaCook6962%40outlook.com</t>
+  </si>
+  <si>
+    <t>H682</t>
+  </si>
+  <si>
+    <t>KellyNeville3537@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a1cc7c5d77ef04c8/KellyNeville3537%40outlook.com</t>
+  </si>
+  <si>
+    <t>H683</t>
+  </si>
+  <si>
+    <t>AndrewPeterson5403@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a76c02bbb6be0053/AndrewPeterson5403%40outlook.com</t>
+  </si>
+  <si>
+    <t>H684</t>
+  </si>
+  <si>
+    <t>RykerHurst2874@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/961717b5c3c337d6/RykerHurst2874%40outlook.com</t>
+  </si>
+  <si>
+    <t>H685</t>
+  </si>
+  <si>
+    <t>MariahSnyder9120@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/3f0b6d6371b8f350/MariahSnyder9120%40outlook.com</t>
+  </si>
+  <si>
+    <t>H686</t>
+  </si>
+  <si>
+    <t>AdonisWalsh7612@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/868427228b97a48d/AdonisWalsh7612%40outlook.com</t>
+  </si>
+  <si>
+    <t>H687</t>
+  </si>
+  <si>
+    <t>EastonMcLean7770@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/b33dbc6e144fa43a/EastonMcLean7770%40outlook.com</t>
+  </si>
+  <si>
+    <t>H688</t>
+  </si>
+  <si>
+    <t>AylaPalmer1168@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/e95b2eb1b8a83843/AylaPalmer1168%40outlook.com</t>
+  </si>
+  <si>
+    <t>H689</t>
+  </si>
+  <si>
+    <t>KellyFoster1426@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/b2e3391b471ca806/KellyFoster1426%40outlook.com</t>
+  </si>
+  <si>
+    <t>H690</t>
+  </si>
+  <si>
+    <t>BentleyWright5142@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/e5a031fe9b32c1d5/BentleyWright5142%40outlook.com</t>
+  </si>
+  <si>
+    <t>H691</t>
+  </si>
+  <si>
+    <t>NathanielMay3081@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/b711db0f4a2f2348/NathanielMay3081%40outlook.com</t>
+  </si>
+  <si>
+    <t>H692</t>
+  </si>
+  <si>
+    <t>JosiahRichardson4709@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/a5ae3dd26c05b3d2/JosiahRichardson4709%40outlook.com</t>
+  </si>
+  <si>
+    <t>H693</t>
+  </si>
+  <si>
+    <t>AriannaAtkins9068@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/d927e4d32ea29735/AriannaAtkins9068%40outlook.com</t>
+  </si>
+  <si>
+    <t>H694</t>
+  </si>
+  <si>
+    <t>ChristineNeville1855@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/e1e1fa53e6f586fe/ChristineNeville1855%40outlook.com</t>
+  </si>
+  <si>
+    <t>H695</t>
+  </si>
+  <si>
+    <t>AsherMize7983@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/2b3645b1e267f1b5/AsherMize7983%40outlook.com</t>
+  </si>
+  <si>
+    <t>H696</t>
+  </si>
+  <si>
+    <t>FinleyMixon2295@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/8d09552187cf63e2/FinleyMixon2295%40outlook.com</t>
+  </si>
+  <si>
+    <t>H697</t>
+  </si>
+  <si>
+    <t>EdwardCarroll7690@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/896bfd7c985c6931/EdwardCarroll7690%40outlook.com</t>
+  </si>
+  <si>
+    <t>H698</t>
+  </si>
+  <si>
+    <t>NancyKelly9879@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/eba8636a01e41664/NancyKelly9879%40outlook.com</t>
+  </si>
+  <si>
+    <t>H699</t>
+  </si>
+  <si>
+    <t>JordanHarding5680@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/be84a0246da720dc/JordanHarding5680%40outlook.com</t>
+  </si>
+  <si>
+    <t>H700</t>
+  </si>
+  <si>
+    <t>MichelleMcLean9625@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/c9b644a5efb65cc0/MichelleMcLean9625%40outlook.com</t>
+  </si>
+  <si>
+    <t>H701</t>
+  </si>
+  <si>
+    <t>TylerNegron1935@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/6a509ef527cbc334/TylerNegron1935%40outlook.com</t>
+  </si>
+  <si>
+    <t>H702</t>
+  </si>
+  <si>
+    <t>EmmettFisher3333@outlook.com</t>
+  </si>
+  <si>
+    <t>https://xiaoheiapi.top/m/1440b3965502a03c/EmmettFisher3333%40outlook.com</t>
   </si>
   <si>
     <t>H603</t>
@@ -58,9 +922,6 @@
     <t>https://xiaoheiapi.top/m/6ab86f6638d4c687/MarenDiaz4881%40outlook.com</t>
   </si>
   <si>
-    <t>Ha112211</t>
-  </si>
-  <si>
     <t>H604</t>
   </si>
   <si>
@@ -86,870 +947,6 @@
   </si>
   <si>
     <t>https://xiaoheiapi.top/m/a09fb4bdb55fc811/KellyFord4968%40outlook.com</t>
-  </si>
-  <si>
-    <t>H607</t>
-  </si>
-  <si>
-    <t>LoganWallace4405@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/976fab075d6a0126/LoganWallace4405%40outlook.com</t>
-  </si>
-  <si>
-    <t>H608</t>
-  </si>
-  <si>
-    <t>DanteIrvine8629@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/4f8abeb02aa34166/DanteIrvine8629%40outlook.com</t>
-  </si>
-  <si>
-    <t>H609</t>
-  </si>
-  <si>
-    <t>CherylMora4203@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/c3d13e1792ca40f8/CherylMora4203%40outlook.com</t>
-  </si>
-  <si>
-    <t>H610</t>
-  </si>
-  <si>
-    <t>MollyNunes2030@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a44ba26ecfcf8260/MollyNunes2030%40outlook.com</t>
-  </si>
-  <si>
-    <t>H611</t>
-  </si>
-  <si>
-    <t>JoeHines3731@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/2ba70e2f8a41697c/JoeHines3731%40outlook.com</t>
-  </si>
-  <si>
-    <t>H612</t>
-  </si>
-  <si>
-    <t>LawrenceStevens6421@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a93be6a787515537/LawrenceStevens6421%40outlook.com</t>
-  </si>
-  <si>
-    <t>H613</t>
-  </si>
-  <si>
-    <t>KellyMunro1477@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/95703dec3be3eb0a/KellyMunro1477%40outlook.com</t>
-  </si>
-  <si>
-    <t>H614</t>
-  </si>
-  <si>
-    <t>JuneMelton5318@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/97b81f7a8ebded3c/JuneMelton5318%40outlook.com</t>
-  </si>
-  <si>
-    <t>H615</t>
-  </si>
-  <si>
-    <t>LyraFrost9345@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/d885bf3213ad91a8/LyraFrost9345%40outlook.com</t>
-  </si>
-  <si>
-    <t>H616</t>
-  </si>
-  <si>
-    <t>IslaBlake1504@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/b7267ae761b3327f/IslaBlake1504%40outlook.com</t>
-  </si>
-  <si>
-    <t>H617</t>
-  </si>
-  <si>
-    <t>LylaAtkins7594@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/e201f4b62ea2255f/LylaAtkins7594%40outlook.com</t>
-  </si>
-  <si>
-    <t>H618</t>
-  </si>
-  <si>
-    <t>JaydenGregory3733@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/0b61165dd2150312/JaydenGregory3733%40outlook.com</t>
-  </si>
-  <si>
-    <t>H619</t>
-  </si>
-  <si>
-    <t>LincolnMize1551@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/783622d9b8364743/LincolnMize1551%40outlook.com</t>
-  </si>
-  <si>
-    <t>H620</t>
-  </si>
-  <si>
-    <t>CarolineAlexander7335@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/820583b7405f2591/CarolineAlexander7335%40outlook.com</t>
-  </si>
-  <si>
-    <t>H621</t>
-  </si>
-  <si>
-    <t>ElizabethMontoya4908@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/124262e54acbdacc/ElizabethMontoya4908%40outlook.com</t>
-  </si>
-  <si>
-    <t>H622</t>
-  </si>
-  <si>
-    <t>MackenzieMercer6362@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/03bbfde8a9ac5b08/MackenzieMercer6362%40outlook.com</t>
-  </si>
-  <si>
-    <t>H623</t>
-  </si>
-  <si>
-    <t>EmmaWiggins6113@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/85d3d404262fb756/EmmaWiggins6113%40outlook.com</t>
-  </si>
-  <si>
-    <t>H624</t>
-  </si>
-  <si>
-    <t>SeanGeddes1993@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/434342602b7ed024/SeanGeddes1993%40outlook.com</t>
-  </si>
-  <si>
-    <t>H625</t>
-  </si>
-  <si>
-    <t>DeanSimpson2150@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/15c7802983d3b125/DeanSimpson2150%40outlook.com</t>
-  </si>
-  <si>
-    <t>H626</t>
-  </si>
-  <si>
-    <t>WyattYoung2899@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/1116d69ded6e51dd/WyattYoung2899%40outlook.com</t>
-  </si>
-  <si>
-    <t>H627</t>
-  </si>
-  <si>
-    <t>HunterMcDonald7149@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/5f0dcc3f5aea4971/HunterMcDonald7149%40outlook.com</t>
-  </si>
-  <si>
-    <t>H628</t>
-  </si>
-  <si>
-    <t>ZoeBell7571@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/83925594ad0cfa42/ZoeBell7571%40outlook.com</t>
-  </si>
-  <si>
-    <t>H629</t>
-  </si>
-  <si>
-    <t>AnnaFerguson1513@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/c0bc17370d47e8b9/AnnaFerguson1513%40outlook.com</t>
-  </si>
-  <si>
-    <t>H630</t>
-  </si>
-  <si>
-    <t>WilliamPickering7944@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/ef0f03f5d771ff23/WilliamPickering7944%40outlook.com</t>
-  </si>
-  <si>
-    <t>H631</t>
-  </si>
-  <si>
-    <t>ZacharyBenson4213@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/0ce5a6063f48a3dd/ZacharyBenson4213%40outlook.com</t>
-  </si>
-  <si>
-    <t>H632</t>
-  </si>
-  <si>
-    <t>LeiaLight4639@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/abf539e7967f47de/LeiaLight4639%40outlook.com</t>
-  </si>
-  <si>
-    <t>H633</t>
-  </si>
-  <si>
-    <t>RyanClarke8467@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a7a55f2aa8d34485/RyanClarke8467%40outlook.com</t>
-  </si>
-  <si>
-    <t>H634</t>
-  </si>
-  <si>
-    <t>HugoFlynn6905@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/adcccd00464b1954/HugoFlynn6905%40outlook.com</t>
-  </si>
-  <si>
-    <t>H635</t>
-  </si>
-  <si>
-    <t>MayaMoriarty5263@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/d28aa5778385cfc1/MayaMoriarty5263%40outlook.com</t>
-  </si>
-  <si>
-    <t>H636</t>
-  </si>
-  <si>
-    <t>AustinMorrison2327@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/ca36692e13ded639/AustinMorrison2327%40outlook.com</t>
-  </si>
-  <si>
-    <t>H637</t>
-  </si>
-  <si>
-    <t>VioletRomero7746@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/38d69e2a356d3778/VioletRomero7746%40outlook.com</t>
-  </si>
-  <si>
-    <t>H638</t>
-  </si>
-  <si>
-    <t>AliceWashington8906@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/bac107909e0132eb/AliceWashington8906%40outlook.com</t>
-  </si>
-  <si>
-    <t>H639</t>
-  </si>
-  <si>
-    <t>VictoriaNeuman9809@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/338c6a11a87c3685/VictoriaNeuman9809%40outlook.com</t>
-  </si>
-  <si>
-    <t>H640</t>
-  </si>
-  <si>
-    <t>LanaWashington2966@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/5ec8fd3cb5e3c2ef/LanaWashington2966%40outlook.com</t>
-  </si>
-  <si>
-    <t>H641</t>
-  </si>
-  <si>
-    <t>WillowMatthews2848@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/3b1935181644bf7d/WillowMatthews2848%40outlook.com</t>
-  </si>
-  <si>
-    <t>H642</t>
-  </si>
-  <si>
-    <t>AbigailLaw5534@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/e081aa542842c22c/AbigailLaw5534%40outlook.com</t>
-  </si>
-  <si>
-    <t>H643</t>
-  </si>
-  <si>
-    <t>DavidMcLaughlin9343@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/fb3582b117260ff1/DavidMcLaughlin9343%40outlook.com</t>
-  </si>
-  <si>
-    <t>H644</t>
-  </si>
-  <si>
-    <t>SophiaBell7584@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/fbb385a074704150/SophiaBell7584%40outlook.com</t>
-  </si>
-  <si>
-    <t>H645</t>
-  </si>
-  <si>
-    <t>RuthCooper5419@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/b7f114faa66e3244/RuthCooper5419%40outlook.com</t>
-  </si>
-  <si>
-    <t>H646</t>
-  </si>
-  <si>
-    <t>PiperDoherty9108@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/adc49bd54472a9b0/PiperDoherty9108%40outlook.com</t>
-  </si>
-  <si>
-    <t>H647</t>
-  </si>
-  <si>
-    <t>RachelNeff2533@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/d171718e17716cf3/RachelNeff2533%40outlook.com</t>
-  </si>
-  <si>
-    <t>H648</t>
-  </si>
-  <si>
-    <t>CarolynFowler4878@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/b3c6c1c00185a5c7/CarolynFowler4878%40outlook.com</t>
-  </si>
-  <si>
-    <t>H649</t>
-  </si>
-  <si>
-    <t>MarenMorales3274@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/18d8597929c74cd8/MarenMorales3274%40outlook.com</t>
-  </si>
-  <si>
-    <t>H650</t>
-  </si>
-  <si>
-    <t>LukeBenson2669@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/83b61b7f53661f16/LukeBenson2669%40outlook.com</t>
-  </si>
-  <si>
-    <t>H651</t>
-  </si>
-  <si>
-    <t>SavannahPollard8686@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/702f833310bc8da4/SavannahPollard8686%40outlook.com</t>
-  </si>
-  <si>
-    <t>H652</t>
-  </si>
-  <si>
-    <t>CarterCaufield7214@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/12c6023b8690a21b/CarterCaufield7214%40outlook.com</t>
-  </si>
-  <si>
-    <t>H653</t>
-  </si>
-  <si>
-    <t>AdonisMartin5227@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/7c57f33406c4857b/AdonisMartin5227%40outlook.com</t>
-  </si>
-  <si>
-    <t>H654</t>
-  </si>
-  <si>
-    <t>AsherHancock6386@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/97c973c0a69cb9fa/AsherHancock6386%40outlook.com</t>
-  </si>
-  <si>
-    <t>H655</t>
-  </si>
-  <si>
-    <t>AbelBaillie5326@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/448b723019d08459/AbelBaillie5326%40outlook.com</t>
-  </si>
-  <si>
-    <t>H656</t>
-  </si>
-  <si>
-    <t>LaylaPerry7131@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/e859b72901cb38f8/LaylaPerry7131%40outlook.com</t>
-  </si>
-  <si>
-    <t>H657</t>
-  </si>
-  <si>
-    <t>JordanPierce3119@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/4fa0bfd02f078af7/JordanPierce3119%40outlook.com</t>
-  </si>
-  <si>
-    <t>H658</t>
-  </si>
-  <si>
-    <t>RykerKelly1119@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/7c110d60bf69610a/RykerKelly1119%40outlook.com</t>
-  </si>
-  <si>
-    <t>H659</t>
-  </si>
-  <si>
-    <t>BenjaminWalsh3768@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/ff2d8b09fcdd6555/BenjaminWalsh3768%40outlook.com</t>
-  </si>
-  <si>
-    <t>H660</t>
-  </si>
-  <si>
-    <t>GraysonHume6696@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/383894259424b103/GraysonHume6696%40outlook.com</t>
-  </si>
-  <si>
-    <t>H661</t>
-  </si>
-  <si>
-    <t>LylaMoriarty3944@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/1fcf7637630df835/LylaMoriarty3944%40outlook.com</t>
-  </si>
-  <si>
-    <t>H662</t>
-  </si>
-  <si>
-    <t>JeremyCole5562@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/6ef58a88b4894c3a/JeremyCole5562%40outlook.com</t>
-  </si>
-  <si>
-    <t>H663</t>
-  </si>
-  <si>
-    <t>RyleeSoto6143@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/9aba92f09bcea28d/RyleeSoto6143%40outlook.com</t>
-  </si>
-  <si>
-    <t>H664</t>
-  </si>
-  <si>
-    <t>BeckettGomez6698@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/b64cf9d4732e1567/BeckettGomez6698%40outlook.com</t>
-  </si>
-  <si>
-    <t>H665</t>
-  </si>
-  <si>
-    <t>PeterNunn3902@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/6d31e04c3d1c1175/PeterNunn3902%40outlook.com</t>
-  </si>
-  <si>
-    <t>H666</t>
-  </si>
-  <si>
-    <t>MarthaNichols8455@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/ee0a1e079316ff94/MarthaNichols8455%40outlook.com</t>
-  </si>
-  <si>
-    <t>H667</t>
-  </si>
-  <si>
-    <t>IsiahBall8960@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/6528cd5fa058e61f/IsiahBall8960%40outlook.com</t>
-  </si>
-  <si>
-    <t>H668</t>
-  </si>
-  <si>
-    <t>MatthewNightingale5815@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/53aabb95400638a6/MatthewNightingale5815%40outlook.com</t>
-  </si>
-  <si>
-    <t>H669</t>
-  </si>
-  <si>
-    <t>DorothyReyes5813@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/5f36dc7d88f1d501/DorothyReyes5813%40outlook.com</t>
-  </si>
-  <si>
-    <t>H670</t>
-  </si>
-  <si>
-    <t>AveryBell8104@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/8e3498489bc3533e/AveryBell8104%40outlook.com</t>
-  </si>
-  <si>
-    <t>H671</t>
-  </si>
-  <si>
-    <t>RachelWilson2467@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/da9a8ba99e71a2ff/RachelWilson2467%40outlook.com</t>
-  </si>
-  <si>
-    <t>H672</t>
-  </si>
-  <si>
-    <t>LydiaKennedy7118@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/4bef06847e27b56d/LydiaKennedy7118%40outlook.com</t>
-  </si>
-  <si>
-    <t>H673</t>
-  </si>
-  <si>
-    <t>IsabellaMonroe8273@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/cb5144690e476600/IsabellaMonroe8273%40outlook.com</t>
-  </si>
-  <si>
-    <t>H674</t>
-  </si>
-  <si>
-    <t>BrendaLambert1930@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a56367f21d956b35/BrendaLambert1930%40outlook.com</t>
-  </si>
-  <si>
-    <t>H675</t>
-  </si>
-  <si>
-    <t>AdamMontgomery1569@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a5c405ae61e24be5/AdamMontgomery1569%40outlook.com</t>
-  </si>
-  <si>
-    <t>H676</t>
-  </si>
-  <si>
-    <t>GeraldBailey8446@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/fe14b32b113ead48/GeraldBailey8446%40outlook.com</t>
-  </si>
-  <si>
-    <t>H677</t>
-  </si>
-  <si>
-    <t>MayaCole6618@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/08c6ac7d75437e03/MayaCole6618%40outlook.com</t>
-  </si>
-  <si>
-    <t>H678</t>
-  </si>
-  <si>
-    <t>FelixMoody8890@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/544e699848eee95e/FelixMoody8890%40outlook.com</t>
-  </si>
-  <si>
-    <t>H679</t>
-  </si>
-  <si>
-    <t>RubyMason4966@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/42fe1b71338caa99/RubyMason4966%40outlook.com</t>
-  </si>
-  <si>
-    <t>H680</t>
-  </si>
-  <si>
-    <t>DavidBurns3205@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/943f6e8d70a54ab6/DavidBurns3205%40outlook.com</t>
-  </si>
-  <si>
-    <t>H681</t>
-  </si>
-  <si>
-    <t>ElianaCook6962@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/008a1face5b54d02/ElianaCook6962%40outlook.com</t>
-  </si>
-  <si>
-    <t>H682</t>
-  </si>
-  <si>
-    <t>KellyNeville3537@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a1cc7c5d77ef04c8/KellyNeville3537%40outlook.com</t>
-  </si>
-  <si>
-    <t>H683</t>
-  </si>
-  <si>
-    <t>AndrewPeterson5403@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a76c02bbb6be0053/AndrewPeterson5403%40outlook.com</t>
-  </si>
-  <si>
-    <t>H684</t>
-  </si>
-  <si>
-    <t>RykerHurst2874@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/961717b5c3c337d6/RykerHurst2874%40outlook.com</t>
-  </si>
-  <si>
-    <t>H685</t>
-  </si>
-  <si>
-    <t>MariahSnyder9120@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/3f0b6d6371b8f350/MariahSnyder9120%40outlook.com</t>
-  </si>
-  <si>
-    <t>H686</t>
-  </si>
-  <si>
-    <t>AdonisWalsh7612@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/868427228b97a48d/AdonisWalsh7612%40outlook.com</t>
-  </si>
-  <si>
-    <t>H687</t>
-  </si>
-  <si>
-    <t>EastonMcLean7770@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/b33dbc6e144fa43a/EastonMcLean7770%40outlook.com</t>
-  </si>
-  <si>
-    <t>H688</t>
-  </si>
-  <si>
-    <t>AylaPalmer1168@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/e95b2eb1b8a83843/AylaPalmer1168%40outlook.com</t>
-  </si>
-  <si>
-    <t>H689</t>
-  </si>
-  <si>
-    <t>KellyFoster1426@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/b2e3391b471ca806/KellyFoster1426%40outlook.com</t>
-  </si>
-  <si>
-    <t>H690</t>
-  </si>
-  <si>
-    <t>BentleyWright5142@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/e5a031fe9b32c1d5/BentleyWright5142%40outlook.com</t>
-  </si>
-  <si>
-    <t>H691</t>
-  </si>
-  <si>
-    <t>NathanielMay3081@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/b711db0f4a2f2348/NathanielMay3081%40outlook.com</t>
-  </si>
-  <si>
-    <t>H692</t>
-  </si>
-  <si>
-    <t>JosiahRichardson4709@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/a5ae3dd26c05b3d2/JosiahRichardson4709%40outlook.com</t>
-  </si>
-  <si>
-    <t>H693</t>
-  </si>
-  <si>
-    <t>AriannaAtkins9068@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/d927e4d32ea29735/AriannaAtkins9068%40outlook.com</t>
-  </si>
-  <si>
-    <t>H694</t>
-  </si>
-  <si>
-    <t>ChristineNeville1855@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/e1e1fa53e6f586fe/ChristineNeville1855%40outlook.com</t>
-  </si>
-  <si>
-    <t>H695</t>
-  </si>
-  <si>
-    <t>AsherMize7983@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/2b3645b1e267f1b5/AsherMize7983%40outlook.com</t>
-  </si>
-  <si>
-    <t>H696</t>
-  </si>
-  <si>
-    <t>FinleyMixon2295@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/8d09552187cf63e2/FinleyMixon2295%40outlook.com</t>
-  </si>
-  <si>
-    <t>H697</t>
-  </si>
-  <si>
-    <t>EdwardCarroll7690@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/896bfd7c985c6931/EdwardCarroll7690%40outlook.com</t>
-  </si>
-  <si>
-    <t>H698</t>
-  </si>
-  <si>
-    <t>NancyKelly9879@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/eba8636a01e41664/NancyKelly9879%40outlook.com</t>
-  </si>
-  <si>
-    <t>H699</t>
-  </si>
-  <si>
-    <t>JordanHarding5680@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/be84a0246da720dc/JordanHarding5680%40outlook.com</t>
-  </si>
-  <si>
-    <t>H700</t>
-  </si>
-  <si>
-    <t>MichelleMcLean9625@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/c9b644a5efb65cc0/MichelleMcLean9625%40outlook.com</t>
-  </si>
-  <si>
-    <t>H701</t>
-  </si>
-  <si>
-    <t>TylerNegron1935@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/6a509ef527cbc334/TylerNegron1935%40outlook.com</t>
-  </si>
-  <si>
-    <t>H702</t>
-  </si>
-  <si>
-    <t>EmmettFisher3333@outlook.com</t>
-  </si>
-  <si>
-    <t>https://xiaoheiapi.top/m/1440b3965502a03c/EmmettFisher3333%40outlook.com</t>
   </si>
 </sst>
 </file>
@@ -1880,10 +1877,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F101"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1899,1408 +1896,1405 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
         <v>27</v>
       </c>
-      <c r="D8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
         <v>28</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>29</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
         <v>30</v>
       </c>
-      <c r="D9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="B10" t="s">
         <v>31</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>32</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
         <v>33</v>
       </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
+      <c r="B11" t="s">
         <v>34</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
         <v>36</v>
       </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
+      <c r="B12" t="s">
         <v>37</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>38</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
+      <c r="B13" t="s">
         <v>40</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
         <v>42</v>
       </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
+      <c r="B14" t="s">
         <v>43</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>44</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
         <v>45</v>
       </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
+      <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>47</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
         <v>48</v>
       </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>49</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="B17" t="s">
         <v>52</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" t="s">
-        <v>54</v>
-      </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" t="s">
-        <v>57</v>
-      </c>
       <c r="D18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B19" t="s">
         <v>58</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
       <c r="D19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
         <v>61</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>62</v>
       </c>
-      <c r="C20" t="s">
-        <v>63</v>
-      </c>
       <c r="D20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21" t="s">
         <v>64</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
       <c r="D21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" t="s">
         <v>67</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>68</v>
       </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" t="s">
         <v>70</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>71</v>
       </c>
-      <c r="C23" t="s">
-        <v>72</v>
-      </c>
       <c r="D23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" t="s">
         <v>73</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>74</v>
       </c>
-      <c r="C24" t="s">
-        <v>75</v>
-      </c>
       <c r="D24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" t="s">
         <v>76</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>77</v>
       </c>
-      <c r="C25" t="s">
-        <v>78</v>
-      </c>
       <c r="D25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" t="s">
         <v>79</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>80</v>
       </c>
-      <c r="C26" t="s">
-        <v>81</v>
-      </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" t="s">
         <v>82</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>83</v>
       </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
+        <v>84</v>
+      </c>
+      <c r="B28" t="s">
         <v>85</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>86</v>
       </c>
-      <c r="C28" t="s">
-        <v>87</v>
-      </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
         <v>88</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>89</v>
       </c>
-      <c r="C29" t="s">
-        <v>90</v>
-      </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
+        <v>90</v>
+      </c>
+      <c r="B30" t="s">
         <v>91</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>92</v>
       </c>
-      <c r="C30" t="s">
-        <v>93</v>
-      </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
         <v>94</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>95</v>
       </c>
-      <c r="C31" t="s">
-        <v>96</v>
-      </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
         <v>97</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>98</v>
       </c>
-      <c r="C32" t="s">
-        <v>99</v>
-      </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
         <v>100</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>101</v>
       </c>
-      <c r="C33" t="s">
-        <v>102</v>
-      </c>
       <c r="D33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" t="s">
         <v>103</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>104</v>
       </c>
-      <c r="C34" t="s">
-        <v>105</v>
-      </c>
       <c r="D34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" t="s">
         <v>106</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>107</v>
       </c>
-      <c r="C35" t="s">
-        <v>108</v>
-      </c>
       <c r="D35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" t="s">
         <v>109</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>110</v>
       </c>
-      <c r="C36" t="s">
-        <v>111</v>
-      </c>
       <c r="D36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" t="s">
         <v>112</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>113</v>
       </c>
-      <c r="C37" t="s">
-        <v>114</v>
-      </c>
       <c r="D37" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
         <v>115</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>116</v>
       </c>
-      <c r="C38" t="s">
-        <v>117</v>
-      </c>
       <c r="D38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" t="s">
         <v>118</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>119</v>
       </c>
-      <c r="C39" t="s">
-        <v>120</v>
-      </c>
       <c r="D39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" t="s">
         <v>121</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>122</v>
       </c>
-      <c r="C40" t="s">
-        <v>123</v>
-      </c>
       <c r="D40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B41" t="s">
         <v>124</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>125</v>
       </c>
-      <c r="C41" t="s">
-        <v>126</v>
-      </c>
       <c r="D41" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" t="s">
         <v>127</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>128</v>
       </c>
-      <c r="C42" t="s">
-        <v>129</v>
-      </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
+        <v>129</v>
+      </c>
+      <c r="B43" t="s">
         <v>130</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>131</v>
       </c>
-      <c r="C43" t="s">
-        <v>132</v>
-      </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
+        <v>132</v>
+      </c>
+      <c r="B44" t="s">
         <v>133</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>134</v>
       </c>
-      <c r="C44" t="s">
-        <v>135</v>
-      </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
+        <v>135</v>
+      </c>
+      <c r="B45" t="s">
         <v>136</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>137</v>
       </c>
-      <c r="C45" t="s">
-        <v>138</v>
-      </c>
       <c r="D45" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
+        <v>138</v>
+      </c>
+      <c r="B46" t="s">
         <v>139</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>140</v>
       </c>
-      <c r="C46" t="s">
-        <v>141</v>
-      </c>
       <c r="D46" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" t="s">
         <v>142</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>143</v>
       </c>
-      <c r="C47" t="s">
-        <v>144</v>
-      </c>
       <c r="D47" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" t="s">
         <v>145</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>146</v>
       </c>
-      <c r="C48" t="s">
-        <v>147</v>
-      </c>
       <c r="D48" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
+        <v>147</v>
+      </c>
+      <c r="B49" t="s">
         <v>148</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>149</v>
       </c>
-      <c r="C49" t="s">
-        <v>150</v>
-      </c>
       <c r="D49" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
+        <v>150</v>
+      </c>
+      <c r="B50" t="s">
         <v>151</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>152</v>
       </c>
-      <c r="C50" t="s">
-        <v>153</v>
-      </c>
       <c r="D50" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" t="s">
         <v>154</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>155</v>
       </c>
-      <c r="C51" t="s">
-        <v>156</v>
-      </c>
       <c r="D51" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
+        <v>156</v>
+      </c>
+      <c r="B52" t="s">
         <v>157</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>158</v>
       </c>
-      <c r="C52" t="s">
-        <v>159</v>
-      </c>
       <c r="D52" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" t="s">
         <v>160</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>161</v>
       </c>
-      <c r="C53" t="s">
-        <v>162</v>
-      </c>
       <c r="D53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" t="s">
         <v>163</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>164</v>
       </c>
-      <c r="C54" t="s">
-        <v>165</v>
-      </c>
       <c r="D54" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" t="s">
         <v>166</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>167</v>
       </c>
-      <c r="C55" t="s">
-        <v>168</v>
-      </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" t="s">
         <v>169</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>170</v>
       </c>
-      <c r="C56" t="s">
-        <v>171</v>
-      </c>
       <c r="D56" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" t="s">
         <v>172</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>173</v>
       </c>
-      <c r="C57" t="s">
-        <v>174</v>
-      </c>
       <c r="D57" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
+        <v>174</v>
+      </c>
+      <c r="B58" t="s">
         <v>175</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>176</v>
       </c>
-      <c r="C58" t="s">
-        <v>177</v>
-      </c>
       <c r="D58" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
+        <v>177</v>
+      </c>
+      <c r="B59" t="s">
         <v>178</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>179</v>
       </c>
-      <c r="C59" t="s">
-        <v>180</v>
-      </c>
       <c r="D59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
+        <v>180</v>
+      </c>
+      <c r="B60" t="s">
         <v>181</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>182</v>
       </c>
-      <c r="C60" t="s">
-        <v>183</v>
-      </c>
       <c r="D60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" t="s">
         <v>184</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>185</v>
       </c>
-      <c r="C61" t="s">
-        <v>186</v>
-      </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
+        <v>186</v>
+      </c>
+      <c r="B62" t="s">
         <v>187</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>188</v>
       </c>
-      <c r="C62" t="s">
-        <v>189</v>
-      </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" t="s">
         <v>190</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>191</v>
       </c>
-      <c r="C63" t="s">
-        <v>192</v>
-      </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
+        <v>192</v>
+      </c>
+      <c r="B64" t="s">
         <v>193</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>194</v>
       </c>
-      <c r="C64" t="s">
-        <v>195</v>
-      </c>
       <c r="D64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
+        <v>195</v>
+      </c>
+      <c r="B65" t="s">
         <v>196</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>197</v>
       </c>
-      <c r="C65" t="s">
-        <v>198</v>
-      </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
+        <v>198</v>
+      </c>
+      <c r="B66" t="s">
         <v>199</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>200</v>
       </c>
-      <c r="C66" t="s">
-        <v>201</v>
-      </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
+        <v>201</v>
+      </c>
+      <c r="B67" t="s">
         <v>202</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>203</v>
       </c>
-      <c r="C67" t="s">
-        <v>204</v>
-      </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
+        <v>204</v>
+      </c>
+      <c r="B68" t="s">
         <v>205</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>206</v>
       </c>
-      <c r="C68" t="s">
-        <v>207</v>
-      </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
+        <v>207</v>
+      </c>
+      <c r="B69" t="s">
         <v>208</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>209</v>
       </c>
-      <c r="C69" t="s">
-        <v>210</v>
-      </c>
       <c r="D69" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
+        <v>210</v>
+      </c>
+      <c r="B70" t="s">
         <v>211</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>212</v>
       </c>
-      <c r="C70" t="s">
-        <v>213</v>
-      </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
+        <v>213</v>
+      </c>
+      <c r="B71" t="s">
         <v>214</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>215</v>
       </c>
-      <c r="C71" t="s">
-        <v>216</v>
-      </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
+        <v>216</v>
+      </c>
+      <c r="B72" t="s">
         <v>217</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>218</v>
       </c>
-      <c r="C72" t="s">
-        <v>219</v>
-      </c>
       <c r="D72" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
+        <v>219</v>
+      </c>
+      <c r="B73" t="s">
         <v>220</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>221</v>
       </c>
-      <c r="C73" t="s">
-        <v>222</v>
-      </c>
       <c r="D73" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
+        <v>222</v>
+      </c>
+      <c r="B74" t="s">
         <v>223</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>224</v>
       </c>
-      <c r="C74" t="s">
-        <v>225</v>
-      </c>
       <c r="D74" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
+        <v>225</v>
+      </c>
+      <c r="B75" t="s">
         <v>226</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>227</v>
       </c>
-      <c r="C75" t="s">
-        <v>228</v>
-      </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
+        <v>228</v>
+      </c>
+      <c r="B76" t="s">
         <v>229</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>230</v>
       </c>
-      <c r="C76" t="s">
-        <v>231</v>
-      </c>
       <c r="D76" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
+        <v>231</v>
+      </c>
+      <c r="B77" t="s">
         <v>232</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>233</v>
       </c>
-      <c r="C77" t="s">
-        <v>234</v>
-      </c>
       <c r="D77" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
+        <v>234</v>
+      </c>
+      <c r="B78" t="s">
         <v>235</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>236</v>
       </c>
-      <c r="C78" t="s">
-        <v>237</v>
-      </c>
       <c r="D78" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
+        <v>237</v>
+      </c>
+      <c r="B79" t="s">
         <v>238</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>239</v>
       </c>
-      <c r="C79" t="s">
-        <v>240</v>
-      </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
+        <v>240</v>
+      </c>
+      <c r="B80" t="s">
         <v>241</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>242</v>
       </c>
-      <c r="C80" t="s">
-        <v>243</v>
-      </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
+        <v>243</v>
+      </c>
+      <c r="B81" t="s">
         <v>244</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>245</v>
       </c>
-      <c r="C81" t="s">
-        <v>246</v>
-      </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
+        <v>246</v>
+      </c>
+      <c r="B82" t="s">
         <v>247</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>248</v>
       </c>
-      <c r="C82" t="s">
-        <v>249</v>
-      </c>
       <c r="D82" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
+        <v>249</v>
+      </c>
+      <c r="B83" t="s">
         <v>250</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>251</v>
       </c>
-      <c r="C83" t="s">
-        <v>252</v>
-      </c>
       <c r="D83" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
+        <v>252</v>
+      </c>
+      <c r="B84" t="s">
         <v>253</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>254</v>
       </c>
-      <c r="C84" t="s">
-        <v>255</v>
-      </c>
       <c r="D84" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
+        <v>255</v>
+      </c>
+      <c r="B85" t="s">
         <v>256</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>257</v>
       </c>
-      <c r="C85" t="s">
-        <v>258</v>
-      </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
+        <v>258</v>
+      </c>
+      <c r="B86" t="s">
         <v>259</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>260</v>
       </c>
-      <c r="C86" t="s">
-        <v>261</v>
-      </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
+        <v>261</v>
+      </c>
+      <c r="B87" t="s">
         <v>262</v>
       </c>
-      <c r="B87" t="s">
+      <c r="C87" t="s">
         <v>263</v>
       </c>
-      <c r="C87" t="s">
-        <v>264</v>
-      </c>
       <c r="D87" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
+        <v>264</v>
+      </c>
+      <c r="B88" t="s">
         <v>265</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>266</v>
       </c>
-      <c r="C88" t="s">
-        <v>267</v>
-      </c>
       <c r="D88" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
+        <v>267</v>
+      </c>
+      <c r="B89" t="s">
         <v>268</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C89" t="s">
         <v>269</v>
       </c>
-      <c r="C89" t="s">
-        <v>270</v>
-      </c>
       <c r="D89" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
+        <v>270</v>
+      </c>
+      <c r="B90" t="s">
         <v>271</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C90" t="s">
         <v>272</v>
       </c>
-      <c r="C90" t="s">
-        <v>273</v>
-      </c>
       <c r="D90" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
+        <v>273</v>
+      </c>
+      <c r="B91" t="s">
         <v>274</v>
       </c>
-      <c r="B91" t="s">
+      <c r="C91" t="s">
         <v>275</v>
       </c>
-      <c r="C91" t="s">
-        <v>276</v>
-      </c>
       <c r="D91" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
+        <v>276</v>
+      </c>
+      <c r="B92" t="s">
         <v>277</v>
       </c>
-      <c r="B92" t="s">
+      <c r="C92" t="s">
         <v>278</v>
       </c>
-      <c r="C92" t="s">
-        <v>279</v>
-      </c>
       <c r="D92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
+        <v>279</v>
+      </c>
+      <c r="B93" t="s">
         <v>280</v>
       </c>
-      <c r="B93" t="s">
+      <c r="C93" t="s">
         <v>281</v>
       </c>
-      <c r="C93" t="s">
-        <v>282</v>
-      </c>
       <c r="D93" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
+        <v>282</v>
+      </c>
+      <c r="B94" t="s">
         <v>283</v>
       </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
         <v>284</v>
       </c>
-      <c r="C94" t="s">
-        <v>285</v>
-      </c>
       <c r="D94" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4">
       <c r="A95" t="s">
+        <v>285</v>
+      </c>
+      <c r="B95" t="s">
         <v>286</v>
       </c>
-      <c r="B95" t="s">
+      <c r="C95" t="s">
         <v>287</v>
       </c>
-      <c r="C95" t="s">
-        <v>288</v>
-      </c>
       <c r="D95" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
+        <v>288</v>
+      </c>
+      <c r="B96" t="s">
         <v>289</v>
       </c>
-      <c r="B96" t="s">
+      <c r="C96" t="s">
         <v>290</v>
       </c>
-      <c r="C96" t="s">
-        <v>291</v>
-      </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
+        <v>291</v>
+      </c>
+      <c r="B97" t="s">
         <v>292</v>
       </c>
-      <c r="B97" t="s">
+      <c r="C97" t="s">
         <v>293</v>
       </c>
-      <c r="C97" t="s">
-        <v>294</v>
-      </c>
       <c r="D97" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
+        <v>294</v>
+      </c>
+      <c r="B98" t="s">
         <v>295</v>
       </c>
-      <c r="B98" t="s">
+      <c r="C98" t="s">
         <v>296</v>
       </c>
-      <c r="C98" t="s">
-        <v>297</v>
-      </c>
       <c r="D98" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
+        <v>297</v>
+      </c>
+      <c r="B99" t="s">
         <v>298</v>
       </c>
-      <c r="B99" t="s">
+      <c r="C99" t="s">
         <v>299</v>
       </c>
-      <c r="C99" t="s">
-        <v>300</v>
-      </c>
       <c r="D99" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
+        <v>300</v>
+      </c>
+      <c r="B100" t="s">
         <v>301</v>
       </c>
-      <c r="B100" t="s">
+      <c r="C100" t="s">
         <v>302</v>
       </c>
-      <c r="C100" t="s">
-        <v>303</v>
-      </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
+        <v>303</v>
+      </c>
+      <c r="B101" t="s">
         <v>304</v>
       </c>
-      <c r="B101" t="s">
+      <c r="C101" t="s">
         <v>305</v>
       </c>
-      <c r="C101" t="s">
-        <v>306</v>
-      </c>
       <c r="D101" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/spiderJapanese/登录数据.xlsx
+++ b/spiderJapanese/登录数据.xlsx
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1030,17 +1030,17 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>H608</t>
+          <t>H672</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>DanteIrvine8629@outlook.com</t>
+          <t>LydiaKennedy7118@outlook.com</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/4f8abeb02aa34166/DanteIrvine8629%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/4bef06847e27b56d/LydiaKennedy7118%40outlook.com</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
@@ -1048,26 +1048,26 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>登录成功，验证失败</t>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>H609</t>
+          <t>H673</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>CherylMora4203@outlook.com</t>
+          <t>IsabellaMonroe8273@outlook.com</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/c3d13e1792ca40f8/CherylMora4203%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/cb5144690e476600/IsabellaMonroe8273%40outlook.com</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -1075,7 +1075,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1084,17 +1084,17 @@
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>H610</t>
+          <t>H674</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>MollyNunes2030@outlook.com</t>
+          <t>BrendaLambert1930@outlook.com</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/a44ba26ecfcf8260/MollyNunes2030%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/a56367f21d956b35/BrendaLambert1930%40outlook.com</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
@@ -1102,7 +1102,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1111,17 +1111,17 @@
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>H611</t>
+          <t>H675</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>JoeHines3731@outlook.com</t>
+          <t>AdamMontgomery1569@outlook.com</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/2ba70e2f8a41697c/JoeHines3731%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/a5c405ae61e24be5/AdamMontgomery1569%40outlook.com</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -1129,7 +1129,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1138,17 +1138,17 @@
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>H612</t>
+          <t>H676</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>LawrenceStevens6421@outlook.com</t>
+          <t>GeraldBailey8446@outlook.com</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/a93be6a787515537/LawrenceStevens6421%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/fe14b32b113ead48/GeraldBailey8446%40outlook.com</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
@@ -1156,7 +1156,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1165,17 +1165,17 @@
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>H613</t>
+          <t>H677</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>KellyMunro1477@outlook.com</t>
+          <t>MayaCole6618@outlook.com</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/95703dec3be3eb0a/KellyMunro1477%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/08c6ac7d75437e03/MayaCole6618%40outlook.com</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
@@ -1183,7 +1183,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1192,17 +1192,17 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>H614</t>
+          <t>H678</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>JuneMelton5318@outlook.com</t>
+          <t>FelixMoody8890@outlook.com</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/97b81f7a8ebded3c/JuneMelton5318%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/544e699848eee95e/FelixMoody8890%40outlook.com</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
@@ -1210,7 +1210,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1219,611 +1219,746 @@
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>H615</t>
+          <t>H679</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>LyraFrost9345@outlook.com</t>
+          <t>RubyMason4966@outlook.com</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/d885bf3213ad91a8/LyraFrost9345%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/42fe1b71338caa99/RubyMason4966%40outlook.com</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>H616</t>
+          <t>H680</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>IslaBlake1504@outlook.com</t>
+          <t>DavidBurns3205@outlook.com</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/b7267ae761b3327f/IslaBlake1504%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/943f6e8d70a54ab6/DavidBurns3205%40outlook.com</t>
         </is>
       </c>
       <c r="D10" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>H617</t>
+          <t>H681</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>LylaAtkins7594@outlook.com</t>
+          <t>ElianaCook6962@outlook.com</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/e201f4b62ea2255f/LylaAtkins7594%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/008a1face5b54d02/ElianaCook6962%40outlook.com</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
-          <t>H618</t>
+          <t>H682</t>
         </is>
       </c>
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>JaydenGregory3733@outlook.com</t>
+          <t>KellyNeville3537@outlook.com</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/0b61165dd2150312/JaydenGregory3733%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/a1cc7c5d77ef04c8/KellyNeville3537%40outlook.com</t>
         </is>
       </c>
       <c r="D12" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="inlineStr">
         <is>
-          <t>H619</t>
+          <t>H683</t>
         </is>
       </c>
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>LincolnMize1551@outlook.com</t>
+          <t>AndrewPeterson5403@outlook.com</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/783622d9b8364743/LincolnMize1551%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/a76c02bbb6be0053/AndrewPeterson5403%40outlook.com</t>
         </is>
       </c>
       <c r="D13" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="inlineStr">
         <is>
-          <t>H620</t>
+          <t>H684</t>
         </is>
       </c>
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>CarolineAlexander7335@outlook.com</t>
+          <t>RykerHurst2874@outlook.com</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/820583b7405f2591/CarolineAlexander7335%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/961717b5c3c337d6/RykerHurst2874%40outlook.com</t>
         </is>
       </c>
       <c r="D14" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="inlineStr">
         <is>
-          <t>H621</t>
+          <t>H685</t>
         </is>
       </c>
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>ElizabethMontoya4908@outlook.com</t>
+          <t>MariahSnyder9120@outlook.com</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/124262e54acbdacc/ElizabethMontoya4908%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/3f0b6d6371b8f350/MariahSnyder9120%40outlook.com</t>
         </is>
       </c>
       <c r="D15" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="inlineStr">
         <is>
-          <t>H622</t>
+          <t>H686</t>
         </is>
       </c>
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>MackenzieMercer6362@outlook.com</t>
+          <t>AdonisWalsh7612@outlook.com</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/03bbfde8a9ac5b08/MackenzieMercer6362%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/868427228b97a48d/AdonisWalsh7612%40outlook.com</t>
         </is>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="inlineStr">
         <is>
-          <t>H623</t>
+          <t>H687</t>
         </is>
       </c>
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>EmmaWiggins6113@outlook.com</t>
+          <t>EastonMcLean7770@outlook.com</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/85d3d404262fb756/EmmaWiggins6113%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/b33dbc6e144fa43a/EastonMcLean7770%40outlook.com</t>
         </is>
       </c>
       <c r="D17" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="inlineStr">
         <is>
-          <t>H624</t>
+          <t>H688</t>
         </is>
       </c>
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>SeanGeddes1993@outlook.com</t>
+          <t>AylaPalmer1168@outlook.com</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/434342602b7ed024/SeanGeddes1993%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/e95b2eb1b8a83843/AylaPalmer1168%40outlook.com</t>
         </is>
       </c>
       <c r="D18" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="inlineStr">
         <is>
-          <t>H625</t>
+          <t>H689</t>
         </is>
       </c>
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>DeanSimpson2150@outlook.com</t>
+          <t>KellyFoster1426@outlook.com</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/15c7802983d3b125/DeanSimpson2150%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/b2e3391b471ca806/KellyFoster1426%40outlook.com</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="inlineStr">
         <is>
-          <t>H626</t>
+          <t>H690</t>
         </is>
       </c>
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>WyattYoung2899@outlook.com</t>
+          <t>BentleyWright5142@outlook.com</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/1116d69ded6e51dd/WyattYoung2899%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/e5a031fe9b32c1d5/BentleyWright5142%40outlook.com</t>
         </is>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="inlineStr">
         <is>
-          <t>H627</t>
+          <t>H691</t>
         </is>
       </c>
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>HunterMcDonald7149@outlook.com</t>
+          <t>NathanielMay3081@outlook.com</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/5f0dcc3f5aea4971/HunterMcDonald7149%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/b711db0f4a2f2348/NathanielMay3081%40outlook.com</t>
         </is>
       </c>
       <c r="D21" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="inlineStr">
         <is>
-          <t>H628</t>
+          <t>H692</t>
         </is>
       </c>
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>ZoeBell7571@outlook.com</t>
+          <t>JosiahRichardson4709@outlook.com</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/83925594ad0cfa42/ZoeBell7571%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/a5ae3dd26c05b3d2/JosiahRichardson4709%40outlook.com</t>
         </is>
       </c>
       <c r="D22" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="inlineStr">
         <is>
-          <t>H629</t>
+          <t>H693</t>
         </is>
       </c>
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>AnnaFerguson1513@outlook.com</t>
+          <t>AriannaAtkins9068@outlook.com</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/c0bc17370d47e8b9/AnnaFerguson1513%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/d927e4d32ea29735/AriannaAtkins9068%40outlook.com</t>
         </is>
       </c>
       <c r="D23" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>H630</t>
+          <t>H694</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>WilliamPickering7944@outlook.com</t>
+          <t>ChristineNeville1855@outlook.com</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/ef0f03f5d771ff23/WilliamPickering7944%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/e1e1fa53e6f586fe/ChristineNeville1855%40outlook.com</t>
         </is>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>H631</t>
+          <t>H695</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>ZacharyBenson4213@outlook.com</t>
+          <t>AsherMize7983@outlook.com</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/0ce5a6063f48a3dd/ZacharyBenson4213%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/2b3645b1e267f1b5/AsherMize7983%40outlook.com</t>
         </is>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>H632</t>
+          <t>H696</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>LeiaLight4639@outlook.com</t>
+          <t>FinleyMixon2295@outlook.com</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/abf539e7967f47de/LeiaLight4639%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/8d09552187cf63e2/FinleyMixon2295%40outlook.com</t>
         </is>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>H633</t>
+          <t>H697</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>RyanClarke8467@outlook.com</t>
+          <t>EdwardCarroll7690@outlook.com</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/a7a55f2aa8d34485/RyanClarke8467%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/896bfd7c985c6931/EdwardCarroll7690%40outlook.com</t>
         </is>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>H634</t>
+          <t>H698</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>HugoFlynn6905@outlook.com</t>
+          <t>NancyKelly9879@outlook.com</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/adcccd00464b1954/HugoFlynn6905%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/eba8636a01e41664/NancyKelly9879%40outlook.com</t>
         </is>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>H635</t>
+          <t>H699</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>MayaMoriarty5263@outlook.com</t>
+          <t>JordanHarding5680@outlook.com</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/d28aa5778385cfc1/MayaMoriarty5263%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/be84a0246da720dc/JordanHarding5680%40outlook.com</t>
         </is>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>H636</t>
+          <t>H700</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>AustinMorrison2327@outlook.com</t>
+          <t>MichelleMcLean9625@outlook.com</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/ca36692e13ded639/AustinMorrison2327%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/c9b644a5efb65cc0/MichelleMcLean9625%40outlook.com</t>
         </is>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>H637</t>
+          <t>H701</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>VioletRomero7746@outlook.com</t>
+          <t>TylerNegron1935@outlook.com</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/38d69e2a356d3778/VioletRomero7746%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/6a509ef527cbc334/TylerNegron1935%40outlook.com</t>
         </is>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>H638</t>
+          <t>H702</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>AliceWashington8906@outlook.com</t>
+          <t>EmmettFisher3333@outlook.com</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/bac107909e0132eb/AliceWashington8906%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/1440b3965502a03c/EmmettFisher3333%40outlook.com</t>
         </is>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>H639</t>
+          <t>H603</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>VictoriaNeuman9809@outlook.com</t>
+          <t>MarenDiaz4881@outlook.com</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/338c6a11a87c3685/VictoriaNeuman9809%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/6ab86f6638d4c687/MarenDiaz4881%40outlook.com</t>
         </is>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>H640</t>
+          <t>H604</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>LanaWashington2966@outlook.com</t>
+          <t>BrooklynWatt1594@outlook.com</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/5ec8fd3cb5e3c2ef/LanaWashington2966%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/fc3a2ad27977d3c6/BrooklynWatt1594%40outlook.com</t>
         </is>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>H641</t>
+          <t>H605</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>WillowMatthews2848@outlook.com</t>
+          <t>MargaretGray6350@outlook.com</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/3b1935181644bf7d/WillowMatthews2848%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/e8f52985eac46559/MargaretGray6350%40outlook.com</t>
         </is>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
           <t>Ha112211</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>H642</t>
+          <t>H606</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>AbigailLaw5534@outlook.com</t>
+          <t>KellyFord4968@outlook.com</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/e081aa542842c22c/AbigailLaw5534%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/a09fb4bdb55fc811/KellyFord4968%40outlook.com</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
@@ -1831,1412 +1966,9 @@
           <t>Ha112211</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="inlineStr">
-        <is>
-          <t>H643</t>
-        </is>
-      </c>
-      <c r="B37" s="0" t="inlineStr">
-        <is>
-          <t>DavidMcLaughlin9343@outlook.com</t>
-        </is>
-      </c>
-      <c r="C37" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/fb3582b117260ff1/DavidMcLaughlin9343%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D37" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="inlineStr">
-        <is>
-          <t>H644</t>
-        </is>
-      </c>
-      <c r="B38" s="0" t="inlineStr">
-        <is>
-          <t>SophiaBell7584@outlook.com</t>
-        </is>
-      </c>
-      <c r="C38" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/fbb385a074704150/SophiaBell7584%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="inlineStr">
-        <is>
-          <t>H645</t>
-        </is>
-      </c>
-      <c r="B39" s="0" t="inlineStr">
-        <is>
-          <t>RuthCooper5419@outlook.com</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b7f114faa66e3244/RuthCooper5419%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D39" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="inlineStr">
-        <is>
-          <t>H646</t>
-        </is>
-      </c>
-      <c r="B40" s="0" t="inlineStr">
-        <is>
-          <t>PiperDoherty9108@outlook.com</t>
-        </is>
-      </c>
-      <c r="C40" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/adc49bd54472a9b0/PiperDoherty9108%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D40" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="inlineStr">
-        <is>
-          <t>H647</t>
-        </is>
-      </c>
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>RachelNeff2533@outlook.com</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/d171718e17716cf3/RachelNeff2533%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="inlineStr">
-        <is>
-          <t>H648</t>
-        </is>
-      </c>
-      <c r="B42" s="0" t="inlineStr">
-        <is>
-          <t>CarolynFowler4878@outlook.com</t>
-        </is>
-      </c>
-      <c r="C42" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b3c6c1c00185a5c7/CarolynFowler4878%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D42" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="inlineStr">
-        <is>
-          <t>H649</t>
-        </is>
-      </c>
-      <c r="B43" s="0" t="inlineStr">
-        <is>
-          <t>MarenMorales3274@outlook.com</t>
-        </is>
-      </c>
-      <c r="C43" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/18d8597929c74cd8/MarenMorales3274%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D43" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="inlineStr">
-        <is>
-          <t>H650</t>
-        </is>
-      </c>
-      <c r="B44" s="0" t="inlineStr">
-        <is>
-          <t>LukeBenson2669@outlook.com</t>
-        </is>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/83b61b7f53661f16/LukeBenson2669%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="inlineStr">
-        <is>
-          <t>H651</t>
-        </is>
-      </c>
-      <c r="B45" s="0" t="inlineStr">
-        <is>
-          <t>SavannahPollard8686@outlook.com</t>
-        </is>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/702f833310bc8da4/SavannahPollard8686%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D45" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="inlineStr">
-        <is>
-          <t>H652</t>
-        </is>
-      </c>
-      <c r="B46" s="0" t="inlineStr">
-        <is>
-          <t>CarterCaufield7214@outlook.com</t>
-        </is>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/12c6023b8690a21b/CarterCaufield7214%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="inlineStr">
-        <is>
-          <t>H653</t>
-        </is>
-      </c>
-      <c r="B47" s="0" t="inlineStr">
-        <is>
-          <t>AdonisMartin5227@outlook.com</t>
-        </is>
-      </c>
-      <c r="C47" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/7c57f33406c4857b/AdonisMartin5227%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D47" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="inlineStr">
-        <is>
-          <t>H654</t>
-        </is>
-      </c>
-      <c r="B48" s="0" t="inlineStr">
-        <is>
-          <t>AsherHancock6386@outlook.com</t>
-        </is>
-      </c>
-      <c r="C48" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/97c973c0a69cb9fa/AsherHancock6386%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D48" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="inlineStr">
-        <is>
-          <t>H655</t>
-        </is>
-      </c>
-      <c r="B49" s="0" t="inlineStr">
-        <is>
-          <t>AbelBaillie5326@outlook.com</t>
-        </is>
-      </c>
-      <c r="C49" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/448b723019d08459/AbelBaillie5326%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D49" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="inlineStr">
-        <is>
-          <t>H656</t>
-        </is>
-      </c>
-      <c r="B50" s="0" t="inlineStr">
-        <is>
-          <t>LaylaPerry7131@outlook.com</t>
-        </is>
-      </c>
-      <c r="C50" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e859b72901cb38f8/LaylaPerry7131%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D50" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="inlineStr">
-        <is>
-          <t>H657</t>
-        </is>
-      </c>
-      <c r="B51" s="0" t="inlineStr">
-        <is>
-          <t>JordanPierce3119@outlook.com</t>
-        </is>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/4fa0bfd02f078af7/JordanPierce3119%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D51" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="inlineStr">
-        <is>
-          <t>H658</t>
-        </is>
-      </c>
-      <c r="B52" s="0" t="inlineStr">
-        <is>
-          <t>RykerKelly1119@outlook.com</t>
-        </is>
-      </c>
-      <c r="C52" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/7c110d60bf69610a/RykerKelly1119%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D52" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="inlineStr">
-        <is>
-          <t>H659</t>
-        </is>
-      </c>
-      <c r="B53" s="0" t="inlineStr">
-        <is>
-          <t>BenjaminWalsh3768@outlook.com</t>
-        </is>
-      </c>
-      <c r="C53" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/ff2d8b09fcdd6555/BenjaminWalsh3768%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D53" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="inlineStr">
-        <is>
-          <t>H660</t>
-        </is>
-      </c>
-      <c r="B54" s="0" t="inlineStr">
-        <is>
-          <t>GraysonHume6696@outlook.com</t>
-        </is>
-      </c>
-      <c r="C54" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/383894259424b103/GraysonHume6696%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D54" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="inlineStr">
-        <is>
-          <t>H661</t>
-        </is>
-      </c>
-      <c r="B55" s="0" t="inlineStr">
-        <is>
-          <t>LylaMoriarty3944@outlook.com</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/1fcf7637630df835/LylaMoriarty3944%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D55" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="inlineStr">
-        <is>
-          <t>H662</t>
-        </is>
-      </c>
-      <c r="B56" s="0" t="inlineStr">
-        <is>
-          <t>JeremyCole5562@outlook.com</t>
-        </is>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/6ef58a88b4894c3a/JeremyCole5562%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D56" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="inlineStr">
-        <is>
-          <t>H663</t>
-        </is>
-      </c>
-      <c r="B57" s="0" t="inlineStr">
-        <is>
-          <t>RyleeSoto6143@outlook.com</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/9aba92f09bcea28d/RyleeSoto6143%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D57" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="inlineStr">
-        <is>
-          <t>H664</t>
-        </is>
-      </c>
-      <c r="B58" s="0" t="inlineStr">
-        <is>
-          <t>BeckettGomez6698@outlook.com</t>
-        </is>
-      </c>
-      <c r="C58" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b64cf9d4732e1567/BeckettGomez6698%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D58" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="inlineStr">
-        <is>
-          <t>H665</t>
-        </is>
-      </c>
-      <c r="B59" s="0" t="inlineStr">
-        <is>
-          <t>PeterNunn3902@outlook.com</t>
-        </is>
-      </c>
-      <c r="C59" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/6d31e04c3d1c1175/PeterNunn3902%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D59" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="0" t="inlineStr">
-        <is>
-          <t>H666</t>
-        </is>
-      </c>
-      <c r="B60" s="0" t="inlineStr">
-        <is>
-          <t>MarthaNichols8455@outlook.com</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/ee0a1e079316ff94/MarthaNichols8455%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D60" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="inlineStr">
-        <is>
-          <t>H667</t>
-        </is>
-      </c>
-      <c r="B61" s="0" t="inlineStr">
-        <is>
-          <t>IsiahBall8960@outlook.com</t>
-        </is>
-      </c>
-      <c r="C61" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/6528cd5fa058e61f/IsiahBall8960%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D61" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="inlineStr">
-        <is>
-          <t>H668</t>
-        </is>
-      </c>
-      <c r="B62" s="0" t="inlineStr">
-        <is>
-          <t>MatthewNightingale5815@outlook.com</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/53aabb95400638a6/MatthewNightingale5815%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D62" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="inlineStr">
-        <is>
-          <t>H669</t>
-        </is>
-      </c>
-      <c r="B63" s="0" t="inlineStr">
-        <is>
-          <t>DorothyReyes5813@outlook.com</t>
-        </is>
-      </c>
-      <c r="C63" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/5f36dc7d88f1d501/DorothyReyes5813%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D63" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="inlineStr">
-        <is>
-          <t>H670</t>
-        </is>
-      </c>
-      <c r="B64" s="0" t="inlineStr">
-        <is>
-          <t>AveryBell8104@outlook.com</t>
-        </is>
-      </c>
-      <c r="C64" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/8e3498489bc3533e/AveryBell8104%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D64" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="inlineStr">
-        <is>
-          <t>H671</t>
-        </is>
-      </c>
-      <c r="B65" s="0" t="inlineStr">
-        <is>
-          <t>RachelWilson2467@outlook.com</t>
-        </is>
-      </c>
-      <c r="C65" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/da9a8ba99e71a2ff/RachelWilson2467%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D65" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="inlineStr">
-        <is>
-          <t>H672</t>
-        </is>
-      </c>
-      <c r="B66" s="0" t="inlineStr">
-        <is>
-          <t>LydiaKennedy7118@outlook.com</t>
-        </is>
-      </c>
-      <c r="C66" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/4bef06847e27b56d/LydiaKennedy7118%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D66" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="inlineStr">
-        <is>
-          <t>H673</t>
-        </is>
-      </c>
-      <c r="B67" s="0" t="inlineStr">
-        <is>
-          <t>IsabellaMonroe8273@outlook.com</t>
-        </is>
-      </c>
-      <c r="C67" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/cb5144690e476600/IsabellaMonroe8273%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D67" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="inlineStr">
-        <is>
-          <t>H674</t>
-        </is>
-      </c>
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>BrendaLambert1930@outlook.com</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a56367f21d956b35/BrendaLambert1930%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D68" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="inlineStr">
-        <is>
-          <t>H675</t>
-        </is>
-      </c>
-      <c r="B69" s="0" t="inlineStr">
-        <is>
-          <t>AdamMontgomery1569@outlook.com</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a5c405ae61e24be5/AdamMontgomery1569%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D69" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="inlineStr">
-        <is>
-          <t>H676</t>
-        </is>
-      </c>
-      <c r="B70" s="0" t="inlineStr">
-        <is>
-          <t>GeraldBailey8446@outlook.com</t>
-        </is>
-      </c>
-      <c r="C70" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/fe14b32b113ead48/GeraldBailey8446%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D70" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="inlineStr">
-        <is>
-          <t>H677</t>
-        </is>
-      </c>
-      <c r="B71" s="0" t="inlineStr">
-        <is>
-          <t>MayaCole6618@outlook.com</t>
-        </is>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/08c6ac7d75437e03/MayaCole6618%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D71" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="inlineStr">
-        <is>
-          <t>H678</t>
-        </is>
-      </c>
-      <c r="B72" s="0" t="inlineStr">
-        <is>
-          <t>FelixMoody8890@outlook.com</t>
-        </is>
-      </c>
-      <c r="C72" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/544e699848eee95e/FelixMoody8890%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D72" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="inlineStr">
-        <is>
-          <t>H679</t>
-        </is>
-      </c>
-      <c r="B73" s="0" t="inlineStr">
-        <is>
-          <t>RubyMason4966@outlook.com</t>
-        </is>
-      </c>
-      <c r="C73" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/42fe1b71338caa99/RubyMason4966%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D73" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="inlineStr">
-        <is>
-          <t>H680</t>
-        </is>
-      </c>
-      <c r="B74" s="0" t="inlineStr">
-        <is>
-          <t>DavidBurns3205@outlook.com</t>
-        </is>
-      </c>
-      <c r="C74" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/943f6e8d70a54ab6/DavidBurns3205%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D74" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="inlineStr">
-        <is>
-          <t>H681</t>
-        </is>
-      </c>
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>ElianaCook6962@outlook.com</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/008a1face5b54d02/ElianaCook6962%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="inlineStr">
-        <is>
-          <t>H682</t>
-        </is>
-      </c>
-      <c r="B76" s="0" t="inlineStr">
-        <is>
-          <t>KellyNeville3537@outlook.com</t>
-        </is>
-      </c>
-      <c r="C76" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a1cc7c5d77ef04c8/KellyNeville3537%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D76" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="inlineStr">
-        <is>
-          <t>H683</t>
-        </is>
-      </c>
-      <c r="B77" s="0" t="inlineStr">
-        <is>
-          <t>AndrewPeterson5403@outlook.com</t>
-        </is>
-      </c>
-      <c r="C77" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a76c02bbb6be0053/AndrewPeterson5403%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D77" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="inlineStr">
-        <is>
-          <t>H684</t>
-        </is>
-      </c>
-      <c r="B78" s="0" t="inlineStr">
-        <is>
-          <t>RykerHurst2874@outlook.com</t>
-        </is>
-      </c>
-      <c r="C78" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/961717b5c3c337d6/RykerHurst2874%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D78" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="inlineStr">
-        <is>
-          <t>H685</t>
-        </is>
-      </c>
-      <c r="B79" s="0" t="inlineStr">
-        <is>
-          <t>MariahSnyder9120@outlook.com</t>
-        </is>
-      </c>
-      <c r="C79" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/3f0b6d6371b8f350/MariahSnyder9120%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D79" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="inlineStr">
-        <is>
-          <t>H686</t>
-        </is>
-      </c>
-      <c r="B80" s="0" t="inlineStr">
-        <is>
-          <t>AdonisWalsh7612@outlook.com</t>
-        </is>
-      </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/868427228b97a48d/AdonisWalsh7612%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D80" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="inlineStr">
-        <is>
-          <t>H687</t>
-        </is>
-      </c>
-      <c r="B81" s="0" t="inlineStr">
-        <is>
-          <t>EastonMcLean7770@outlook.com</t>
-        </is>
-      </c>
-      <c r="C81" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b33dbc6e144fa43a/EastonMcLean7770%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D81" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="inlineStr">
-        <is>
-          <t>H688</t>
-        </is>
-      </c>
-      <c r="B82" s="0" t="inlineStr">
-        <is>
-          <t>AylaPalmer1168@outlook.com</t>
-        </is>
-      </c>
-      <c r="C82" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e95b2eb1b8a83843/AylaPalmer1168%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D82" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="inlineStr">
-        <is>
-          <t>H689</t>
-        </is>
-      </c>
-      <c r="B83" s="0" t="inlineStr">
-        <is>
-          <t>KellyFoster1426@outlook.com</t>
-        </is>
-      </c>
-      <c r="C83" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b2e3391b471ca806/KellyFoster1426%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D83" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="inlineStr">
-        <is>
-          <t>H690</t>
-        </is>
-      </c>
-      <c r="B84" s="0" t="inlineStr">
-        <is>
-          <t>BentleyWright5142@outlook.com</t>
-        </is>
-      </c>
-      <c r="C84" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e5a031fe9b32c1d5/BentleyWright5142%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D84" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="inlineStr">
-        <is>
-          <t>H691</t>
-        </is>
-      </c>
-      <c r="B85" s="0" t="inlineStr">
-        <is>
-          <t>NathanielMay3081@outlook.com</t>
-        </is>
-      </c>
-      <c r="C85" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b711db0f4a2f2348/NathanielMay3081%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D85" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="inlineStr">
-        <is>
-          <t>H692</t>
-        </is>
-      </c>
-      <c r="B86" s="0" t="inlineStr">
-        <is>
-          <t>JosiahRichardson4709@outlook.com</t>
-        </is>
-      </c>
-      <c r="C86" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a5ae3dd26c05b3d2/JosiahRichardson4709%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D86" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="0" t="inlineStr">
-        <is>
-          <t>H693</t>
-        </is>
-      </c>
-      <c r="B87" s="0" t="inlineStr">
-        <is>
-          <t>AriannaAtkins9068@outlook.com</t>
-        </is>
-      </c>
-      <c r="C87" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/d927e4d32ea29735/AriannaAtkins9068%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D87" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="0" t="inlineStr">
-        <is>
-          <t>H694</t>
-        </is>
-      </c>
-      <c r="B88" s="0" t="inlineStr">
-        <is>
-          <t>ChristineNeville1855@outlook.com</t>
-        </is>
-      </c>
-      <c r="C88" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e1e1fa53e6f586fe/ChristineNeville1855%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D88" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="0" t="inlineStr">
-        <is>
-          <t>H695</t>
-        </is>
-      </c>
-      <c r="B89" s="0" t="inlineStr">
-        <is>
-          <t>AsherMize7983@outlook.com</t>
-        </is>
-      </c>
-      <c r="C89" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/2b3645b1e267f1b5/AsherMize7983%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D89" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="0" t="inlineStr">
-        <is>
-          <t>H696</t>
-        </is>
-      </c>
-      <c r="B90" s="0" t="inlineStr">
-        <is>
-          <t>FinleyMixon2295@outlook.com</t>
-        </is>
-      </c>
-      <c r="C90" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/8d09552187cf63e2/FinleyMixon2295%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D90" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="0" t="inlineStr">
-        <is>
-          <t>H697</t>
-        </is>
-      </c>
-      <c r="B91" s="0" t="inlineStr">
-        <is>
-          <t>EdwardCarroll7690@outlook.com</t>
-        </is>
-      </c>
-      <c r="C91" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/896bfd7c985c6931/EdwardCarroll7690%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D91" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="0" t="inlineStr">
-        <is>
-          <t>H698</t>
-        </is>
-      </c>
-      <c r="B92" s="0" t="inlineStr">
-        <is>
-          <t>NancyKelly9879@outlook.com</t>
-        </is>
-      </c>
-      <c r="C92" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/eba8636a01e41664/NancyKelly9879%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D92" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="0" t="inlineStr">
-        <is>
-          <t>H699</t>
-        </is>
-      </c>
-      <c r="B93" s="0" t="inlineStr">
-        <is>
-          <t>JordanHarding5680@outlook.com</t>
-        </is>
-      </c>
-      <c r="C93" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/be84a0246da720dc/JordanHarding5680%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D93" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="0" t="inlineStr">
-        <is>
-          <t>H700</t>
-        </is>
-      </c>
-      <c r="B94" s="0" t="inlineStr">
-        <is>
-          <t>MichelleMcLean9625@outlook.com</t>
-        </is>
-      </c>
-      <c r="C94" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/c9b644a5efb65cc0/MichelleMcLean9625%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D94" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="0" t="inlineStr">
-        <is>
-          <t>H701</t>
-        </is>
-      </c>
-      <c r="B95" s="0" t="inlineStr">
-        <is>
-          <t>TylerNegron1935@outlook.com</t>
-        </is>
-      </c>
-      <c r="C95" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/6a509ef527cbc334/TylerNegron1935%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D95" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="0" t="inlineStr">
-        <is>
-          <t>H702</t>
-        </is>
-      </c>
-      <c r="B96" s="0" t="inlineStr">
-        <is>
-          <t>EmmettFisher3333@outlook.com</t>
-        </is>
-      </c>
-      <c r="C96" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/1440b3965502a03c/EmmettFisher3333%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D96" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="0" t="inlineStr">
-        <is>
-          <t>H603</t>
-        </is>
-      </c>
-      <c r="B97" s="0" t="inlineStr">
-        <is>
-          <t>MarenDiaz4881@outlook.com</t>
-        </is>
-      </c>
-      <c r="C97" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/6ab86f6638d4c687/MarenDiaz4881%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D97" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="0" t="inlineStr">
-        <is>
-          <t>H604</t>
-        </is>
-      </c>
-      <c r="B98" s="0" t="inlineStr">
-        <is>
-          <t>BrooklynWatt1594@outlook.com</t>
-        </is>
-      </c>
-      <c r="C98" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/fc3a2ad27977d3c6/BrooklynWatt1594%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D98" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="0" t="inlineStr">
-        <is>
-          <t>H605</t>
-        </is>
-      </c>
-      <c r="B99" s="0" t="inlineStr">
-        <is>
-          <t>MargaretGray6350@outlook.com</t>
-        </is>
-      </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e8f52985eac46559/MargaretGray6350%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D99" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="0" t="inlineStr">
-        <is>
-          <t>H606</t>
-        </is>
-      </c>
-      <c r="B100" s="0" t="inlineStr">
-        <is>
-          <t>KellyFord4968@outlook.com</t>
-        </is>
-      </c>
-      <c r="C100" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a09fb4bdb55fc811/KellyFord4968%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D100" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>登录失败</t>
         </is>
       </c>
     </row>

--- a/spiderJapanese/登录数据.xlsx
+++ b/spiderJapanese/登录数据.xlsx
@@ -1048,7 +1048,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1075,7 +1075,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1102,7 +1102,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1129,7 +1129,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1156,7 +1156,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1183,7 +1183,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1210,7 +1210,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1237,7 +1237,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1264,7 +1264,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1291,7 +1291,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1318,7 +1318,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1345,7 +1345,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1372,7 +1372,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1399,7 +1399,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1426,7 +1426,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1453,7 +1453,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1480,7 +1480,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1507,7 +1507,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1534,7 +1534,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1561,7 +1561,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1588,7 +1588,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1615,7 +1615,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1642,7 +1642,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1669,7 +1669,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1696,7 +1696,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1723,7 +1723,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1750,7 +1750,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1777,7 +1777,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1804,7 +1804,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1831,7 +1831,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1858,7 +1858,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1885,7 +1885,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1912,7 +1912,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1939,7 +1939,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>
@@ -1966,7 +1966,7 @@
           <t>Ha112211</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t>登录失败</t>
         </is>

--- a/spiderJapanese/登录数据.xlsx
+++ b/spiderJapanese/登录数据.xlsx
@@ -1002,8 +1002,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -1030,17 +1030,17 @@
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>H672</t>
+          <t>H661</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>LydiaKennedy7118@outlook.com</t>
+          <t>LylaMoriarty3944@outlook.com</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/4bef06847e27b56d/LydiaKennedy7118%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/1fcf7637630df835/LylaMoriarty3944%40outlook.com</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
@@ -1050,24 +1050,29 @@
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>登录失败</t>
+          <t>登录成功，验证成功</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>09025032755</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>H673</t>
+          <t>H662</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>IsabellaMonroe8273@outlook.com</t>
+          <t>JeremyCole5562@outlook.com</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>https://xiaoheiapi.top/m/cb5144690e476600/IsabellaMonroe8273%40outlook.com</t>
+          <t>https://xiaoheiapi.top/m/6ef58a88b4894c3a/JeremyCole5562%40outlook.com</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
@@ -1077,898 +1082,7 @@
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>H674</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>BrendaLambert1930@outlook.com</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a56367f21d956b35/BrendaLambert1930%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F4" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>H675</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>AdamMontgomery1569@outlook.com</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a5c405ae61e24be5/AdamMontgomery1569%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>H676</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>GeraldBailey8446@outlook.com</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/fe14b32b113ead48/GeraldBailey8446%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F6" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>H677</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>MayaCole6618@outlook.com</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/08c6ac7d75437e03/MayaCole6618%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F7" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>H678</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>FelixMoody8890@outlook.com</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/544e699848eee95e/FelixMoody8890%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>H679</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>RubyMason4966@outlook.com</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/42fe1b71338caa99/RubyMason4966%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>H680</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>DavidBurns3205@outlook.com</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/943f6e8d70a54ab6/DavidBurns3205%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>H681</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>ElianaCook6962@outlook.com</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/008a1face5b54d02/ElianaCook6962%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>H682</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>KellyNeville3537@outlook.com</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a1cc7c5d77ef04c8/KellyNeville3537%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>H683</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>AndrewPeterson5403@outlook.com</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a76c02bbb6be0053/AndrewPeterson5403%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>H684</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>RykerHurst2874@outlook.com</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/961717b5c3c337d6/RykerHurst2874%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>H685</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>MariahSnyder9120@outlook.com</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/3f0b6d6371b8f350/MariahSnyder9120%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D15" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>H686</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>AdonisWalsh7612@outlook.com</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/868427228b97a48d/AdonisWalsh7612%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D16" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F16" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>H687</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>EastonMcLean7770@outlook.com</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b33dbc6e144fa43a/EastonMcLean7770%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D17" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F17" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>H688</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>AylaPalmer1168@outlook.com</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e95b2eb1b8a83843/AylaPalmer1168%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F18" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>H689</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>KellyFoster1426@outlook.com</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b2e3391b471ca806/KellyFoster1426%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D19" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F19" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
-        <is>
-          <t>H690</t>
-        </is>
-      </c>
-      <c r="B20" s="0" t="inlineStr">
-        <is>
-          <t>BentleyWright5142@outlook.com</t>
-        </is>
-      </c>
-      <c r="C20" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e5a031fe9b32c1d5/BentleyWright5142%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
-        <is>
-          <t>H691</t>
-        </is>
-      </c>
-      <c r="B21" s="0" t="inlineStr">
-        <is>
-          <t>NathanielMay3081@outlook.com</t>
-        </is>
-      </c>
-      <c r="C21" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/b711db0f4a2f2348/NathanielMay3081%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D21" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
-        <is>
-          <t>H692</t>
-        </is>
-      </c>
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>JosiahRichardson4709@outlook.com</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a5ae3dd26c05b3d2/JosiahRichardson4709%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D22" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
-        <is>
-          <t>H693</t>
-        </is>
-      </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>AriannaAtkins9068@outlook.com</t>
-        </is>
-      </c>
-      <c r="C23" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/d927e4d32ea29735/AriannaAtkins9068%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D23" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
-        <is>
-          <t>H694</t>
-        </is>
-      </c>
-      <c r="B24" s="0" t="inlineStr">
-        <is>
-          <t>ChristineNeville1855@outlook.com</t>
-        </is>
-      </c>
-      <c r="C24" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e1e1fa53e6f586fe/ChristineNeville1855%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D24" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
-        <is>
-          <t>H695</t>
-        </is>
-      </c>
-      <c r="B25" s="0" t="inlineStr">
-        <is>
-          <t>AsherMize7983@outlook.com</t>
-        </is>
-      </c>
-      <c r="C25" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/2b3645b1e267f1b5/AsherMize7983%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D25" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="inlineStr">
-        <is>
-          <t>H696</t>
-        </is>
-      </c>
-      <c r="B26" s="0" t="inlineStr">
-        <is>
-          <t>FinleyMixon2295@outlook.com</t>
-        </is>
-      </c>
-      <c r="C26" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/8d09552187cf63e2/FinleyMixon2295%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="inlineStr">
-        <is>
-          <t>H697</t>
-        </is>
-      </c>
-      <c r="B27" s="0" t="inlineStr">
-        <is>
-          <t>EdwardCarroll7690@outlook.com</t>
-        </is>
-      </c>
-      <c r="C27" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/896bfd7c985c6931/EdwardCarroll7690%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F27" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="inlineStr">
-        <is>
-          <t>H698</t>
-        </is>
-      </c>
-      <c r="B28" s="0" t="inlineStr">
-        <is>
-          <t>NancyKelly9879@outlook.com</t>
-        </is>
-      </c>
-      <c r="C28" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/eba8636a01e41664/NancyKelly9879%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="inlineStr">
-        <is>
-          <t>H699</t>
-        </is>
-      </c>
-      <c r="B29" s="0" t="inlineStr">
-        <is>
-          <t>JordanHarding5680@outlook.com</t>
-        </is>
-      </c>
-      <c r="C29" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/be84a0246da720dc/JordanHarding5680%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D29" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F29" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="inlineStr">
-        <is>
-          <t>H700</t>
-        </is>
-      </c>
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t>MichelleMcLean9625@outlook.com</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/c9b644a5efb65cc0/MichelleMcLean9625%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F30" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="inlineStr">
-        <is>
-          <t>H701</t>
-        </is>
-      </c>
-      <c r="B31" s="0" t="inlineStr">
-        <is>
-          <t>TylerNegron1935@outlook.com</t>
-        </is>
-      </c>
-      <c r="C31" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/6a509ef527cbc334/TylerNegron1935%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F31" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="inlineStr">
-        <is>
-          <t>H702</t>
-        </is>
-      </c>
-      <c r="B32" s="0" t="inlineStr">
-        <is>
-          <t>EmmettFisher3333@outlook.com</t>
-        </is>
-      </c>
-      <c r="C32" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/1440b3965502a03c/EmmettFisher3333%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D32" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F32" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="inlineStr">
-        <is>
-          <t>H603</t>
-        </is>
-      </c>
-      <c r="B33" s="0" t="inlineStr">
-        <is>
-          <t>MarenDiaz4881@outlook.com</t>
-        </is>
-      </c>
-      <c r="C33" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/6ab86f6638d4c687/MarenDiaz4881%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D33" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F33" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="inlineStr">
-        <is>
-          <t>H604</t>
-        </is>
-      </c>
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t>BrooklynWatt1594@outlook.com</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/fc3a2ad27977d3c6/BrooklynWatt1594%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F34" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="inlineStr">
-        <is>
-          <t>H605</t>
-        </is>
-      </c>
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t>MargaretGray6350@outlook.com</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/e8f52985eac46559/MargaretGray6350%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F35" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="inlineStr">
-        <is>
-          <t>H606</t>
-        </is>
-      </c>
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>KellyFord4968@outlook.com</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>https://xiaoheiapi.top/m/a09fb4bdb55fc811/KellyFord4968%40outlook.com</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>Ha112211</t>
-        </is>
-      </c>
-      <c r="F36" s="0" t="inlineStr">
-        <is>
-          <t>登录失败</t>
+          <t>登录成功，验证失败</t>
         </is>
       </c>
     </row>
